--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_coquimbo.xlsx
@@ -375,151 +375,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C2">
-        <v>233851</v>
+        <v>94.41335767078608</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="C3">
-        <v>209030</v>
+        <v>94.35066535239034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C4">
-        <v>112747</v>
+        <v>93.83385407094283</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="C5">
-        <v>31953</v>
+        <v>93.83067577828398</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="C6">
-        <v>31552</v>
+        <v>93.29655750296767</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="C7">
-        <v>30339</v>
+        <v>93.12180143295804</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C8">
-        <v>28068</v>
+        <v>92.83943817130267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="C9">
-        <v>24414</v>
+        <v>92.41936144923972</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Paihuano</t>
         </is>
       </c>
       <c r="C10">
-        <v>15315</v>
+        <v>92.0366708610462</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="C11">
-        <v>13361</v>
+        <v>91.62350821886963</v>
       </c>
     </row>
     <row r="12">
@@ -534,67 +534,67 @@
         </is>
       </c>
       <c r="C12">
-        <v>11986</v>
+        <v>90.63823351482154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C13">
-        <v>10211</v>
+        <v>90.41943173764577</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paihuano</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="C14">
-        <v>5120</v>
+        <v>90.21174477696216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C15">
-        <v>4943</v>
+        <v>88.16481490557715</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="C16">
-        <v>4549</v>
+        <v>82.96816702389458</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C490"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -595,6 +595,7116 @@
       </c>
       <c r="C16">
         <v>82.96816702389458</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>50.06049606775559</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>48.60199188491332</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>48.57688516510596</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>48.28573423643601</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>48.08276385725133</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>47.94268167860798</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>47.7669546039331</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>47.53284059965888</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>47.11486607945353</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>46.8805170711272</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>46.74867652008935</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>46.65160926030492</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>46.2170682278766</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>46.09076165121332</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>46.06689946700974</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>45.77378018728437</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>45.74791192103265</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>45.51863762662916</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>45.43843824495844</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>45.40643999099302</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>45.37205081669691</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>45.26618269812462</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>45.17911975435005</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>45.01082326653167</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>44.98099349268733</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>44.92180478159266</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>43.82551401127252</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>43.81736956432641</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>43.56013551665725</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>43.54109937460726</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>43.2422171602126</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>42.76737309019222</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>42.64617727894798</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>42.31463631078062</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>41.97757765116707</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>41.82994786985439</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>41.52137382679618</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>39.76677606312408</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>39.14265301262206</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>38.63244014110936</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>37.77140648154113</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>36.26674407995687</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>36.14624505928854</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>36.0329703569268</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>35.9467758444217</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>33.52187028657617</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>28.45445240532242</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>27.29885057471265</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>25.51497800432931</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>24.1350428451775</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>24.0894657458125</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>23.72202056866304</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>23.23906757200001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>23.22592490590287</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>22.871259175607</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>22.45649948822927</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.0541825484651</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>22.01080837649178</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>21.69703872437358</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>21.26447344238192</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>21.10645638245441</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>21.06230472339643</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>20.9273095454228</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>20.79463724600237</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>20.52849182095991</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>20.52126036087256</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>20.52012148823083</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>20.00985707244948</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>19.50870010235414</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>19.35306009924646</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>19.2674322600015</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>19.2672741078208</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>18.68398216583381</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>18.35879743716116</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>17.78915046059365</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>17.77809147374365</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>17.28675136116152</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>17.26834718245933</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>16.55844155844156</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>16.34906231094979</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>16.12439331296063</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>16.05229722529612</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>16.0460021905805</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>15.97294951973428</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>15.76596862568491</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>15.74254166791346</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>15.58511594463419</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>15.50578149093473</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>15.41459957476967</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>15.40944231779629</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>15.2177239205606</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>15.05481460791844</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>15.00511770726714</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>14.8627558982833</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>14.83666061705989</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>14.73503012418542</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>14.72332015810277</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>14.54403869011025</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>14.46188683864255</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>14.3675799172834</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>14.34185941627472</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>14.32680208520582</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>14.29976638386819</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>14.29142333633687</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>14.28863868986694</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>14.0931152255977</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>14.06803207112805</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>14.05385466617484</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>14.00911161731207</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>13.92077478764785</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>13.83636891454251</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>13.69992961840938</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>13.65204534253327</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>13.6028419464952</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>13.59649122807017</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>13.54799969976732</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>13.41614906832298</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>13.13454903893544</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>13.05826134901672</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>13.02751111397462</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>13.00317067745426</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>12.98331898848313</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>12.97860866438972</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>12.93103448275862</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>12.92960852784415</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>12.86258633007859</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>12.84620580950237</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>12.84299350668781</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>12.83699011597662</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>12.83480136616933</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>12.78714235625445</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>12.77716269188186</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>12.77578873282536</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>12.61649599110899</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>12.57994430674133</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>12.52814738996929</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>12.52007541372809</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>12.51309266112702</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>12.46698022034663</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>12.45997785690775</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>12.4390316885604</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>12.42607195662888</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>12.36280175417025</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>12.35763097949886</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>12.35742518351214</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>12.33363581367211</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>12.30590812447651</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>12.30338777979431</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>12.25877596030142</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>12.2236203487327</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>12.18580581567275</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>12.17870073910051</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>12.13602402066895</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>12.11803844258255</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>12.11180124223602</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>12.05667248079807</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>12.05391040242976</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>12.04174988724953</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>11.96991347146146</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>11.96781479390175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>11.95398166456948</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>11.94050694783884</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>11.89356355904903</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>11.88909792152856</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>11.88029361942405</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>11.86369666922701</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>11.80783464841841</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>11.71282744126698</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>11.67983826502481</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>11.67425968109339</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>11.66701576947246</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>11.64662321368463</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>11.6190241498275</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>11.61525182016062</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>11.59446341901852</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>11.49604852049256</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>11.44091159713288</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>11.423853486452</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>11.39424006185168</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>11.32331197634303</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>11.30520266182698</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>11.28879892037787</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>11.24553465110741</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>11.19308168367556</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>11.18071374335611</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>11.14684800588127</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>11.0389770072544</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>11.01478645950612</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>10.93142272262027</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>10.8580106302202</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>10.80106302201974</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>10.79576086833583</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>10.74718526100307</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>10.61264822134387</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>10.57924984875983</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>10.52200614124872</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>10.52200614124872</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>10.34749267652681</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>10.09803921568627</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>9.514566960387393</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>7.792854099825443</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>7.441016333938294</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>7.362467254108121</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>7.078610152784623</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>6.036982153211778</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>5.773574251835122</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>5.772773797338792</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>5.500119075970469</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>4.947018235584031</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>4.764065335753176</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>4.692678034858601</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>4.019365007881108</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>3.775564572318538</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>3.762644159525804</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>3.707543648654253</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>3.540372670807453</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>3.442577802258331</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>3.100176064966842</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>2.953704350254871</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>2.834556747600226</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>2.771450265755505</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>2.676950998185118</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>2.673730901922129</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>2.588531367966924</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>2.518148820326679</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>2.514090656505517</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>2.481161551185444</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>2.436028659160696</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>2.341814906552578</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>2.333702200909873</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>2.274337993685974</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>2.272366436453124</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>2.233201581027668</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>2.220956719817768</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>2.105327580403317</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>2.091767881241565</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>2.085257669382415</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>1.997067243907548</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>1.922129127649088</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>1.858378979122013</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>1.829006906406287</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>1.828707958095938</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>1.822323462414579</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>1.707946336429309</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>1.707711666367068</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>1.696180483556588</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>1.67755010132853</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>1.648517846339988</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>1.639785750620904</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>1.635858439242506</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>1.63572872633707</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>1.613515565679575</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>1.596724667349028</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>1.555783009211873</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>1.462534630500612</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>1.441862371408664</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>1.405985319028797</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>1.389669095885659</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>1.376285541439806</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>1.340001587679606</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>1.339207747876479</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>1.337250221855014</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>1.330455511887121</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>1.324012628052316</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>1.18193505577904</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>1.164549304295221</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>1.162940532182205</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>1.149425287356322</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>1.14310273975185</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>1.104162302881594</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>1.078828292450583</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>1.077125503783323</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>1.047430830039526</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>1.036785136648281</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>1.027639971651311</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>1.005747126436782</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>0.9775853641505482</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>0.9566371063473221</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>0.9491268033409264</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>0.9316770186335404</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>0.8808197015998562</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>0.8802456499488229</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>0.8665678757811996</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>0.8454328248483735</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>0.8393829401088929</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>0.8242589231699939</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>0.8215697346132129</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>0.8075613682547702</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>0.7910160252469364</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>0.7909401402121158</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>0.7883337166296566</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>0.7730991518426781</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>0.7602602925069261</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>0.756634669678148</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>0.7516017742730409</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>0.7318171582976807</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>0.7280458733329038</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>0.7086391869000565</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>0.6982752601075344</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>0.6959301610721751</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>0.6926513381695971</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>0.6885155604516662</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>0.6773270023043083</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>0.6708325675427311</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>0.6615025205951064</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>0.629587803500847</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>0.6267357201831419</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>0.6264236902050114</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>0.6229828116790512</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>0.6117240861667792</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>0.6111810174366349</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>0.603597455917781</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>0.5932051051590869</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>0.5844732090945255</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>0.5791030064070971</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>0.5789376952766035</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>0.5737940079511455</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>0.5569325866764588</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>0.5376719502828015</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>0.5356234477393099</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>0.5347593582887701</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>0.5322415557830092</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>0.5315110098709187</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>0.5307735742518351</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>0.5298176441596846</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>0.5254071905726938</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>0.5179013735645125</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>0.5171516876281403</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>0.5167236924795755</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>0.5125284738041003</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>0.5117707267144319</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>0.5089878229495522</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>0.5066426480522405</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>0.5018513418403255</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>0.5008401983687856</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>0.4987912726827626</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>0.4853496314937983</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>0.4673737192162502</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>0.4647731464404279</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>0.4647731464404279</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>0.4594743613306377</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>0.4555808656036446</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>0.4545454545454545</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>0.4503582395087001</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>0.4498301661617553</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>0.4488989271597967</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>0.4365983295368261</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>0.434894658849301</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>0.4314697512163775</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>0.431421894661154</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>0.4262469773351367</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>0.425086249383933</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>0.4227164124241867</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>0.4176157934700076</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>0.4159310571830396</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>0.4069891979558738</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>0.4049996508623699</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>0.4043374379709612</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>0.4039291287983108</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>0.3889457523029683</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>0.3774941578285098</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>0.3770686404580686</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>0.3770310302522517</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>0.3758008871365204</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>0.3631031352559179</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>0.3629764065335753</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>0.3613777526821005</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>0.360668185269552</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>0.360668185269552</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>0.3449975357318876</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C387">
+        <v>0.3441156228492774</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C388">
+        <v>0.3415423332734136</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C389">
+        <v>0.341514673872251</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C390">
+        <v>0.3400110273846719</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C391">
+        <v>0.3393665158371041</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C392">
+        <v>0.3388368654509611</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C393">
+        <v>0.3377617653681603</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C394">
+        <v>0.3275332650972365</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C395">
+        <v>0.3275332650972365</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C396">
+        <v>0.3221441917402229</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C397">
+        <v>0.3216320529314464</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C398">
+        <v>0.3212066196494658</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C399">
+        <v>0.318865527275708</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C400">
+        <v>0.3142238670483904</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C401">
+        <v>0.3141941843272548</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C402">
+        <v>0.3124425657048337</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C403">
+        <v>0.3080335140463282</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C404">
+        <v>0.307738497335435</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C405">
+        <v>0.299230976390676</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C406">
+        <v>0.2932756092451644</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C407">
+        <v>0.2865916069600819</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C408">
+        <v>0.2865916069600819</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C409">
+        <v>0.2722323049001815</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C410">
+        <v>0.2696386841632213</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C411">
+        <v>0.2663155689877016</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C412">
+        <v>0.264670296430732</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C413">
+        <v>0.2573056423451571</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C414">
+        <v>0.2516627718856732</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C415">
+        <v>0.2516627718856732</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C416">
+        <v>0.2467729688686409</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C417">
+        <v>0.2439390527658936</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C418">
+        <v>0.240266140956136</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C419">
+        <v>0.2334001615847273</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C420">
+        <v>0.2214216017413495</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C421">
+        <v>0.2205476934387061</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C422">
+        <v>0.2205476934387061</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C423">
+        <v>0.202499825431185</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C424">
+        <v>0.199439759013433</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C425">
+        <v>0.1909807787087235</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C426">
+        <v>0.1885155151261259</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C427">
+        <v>0.1868436312093293</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C428">
+        <v>0.1848201084277969</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C429">
+        <v>0.1735539663065921</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C430">
+        <v>0.1675693467787785</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C431">
+        <v>0.1654107700790296</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C432">
+        <v>0.161584727250965</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C433">
+        <v>0.1556001077231515</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C434">
+        <v>0.1518602885345482</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C435">
+        <v>0.143295803480041</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C436">
+        <v>0.1407631812478962</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C437">
+        <v>0.1328777524677297</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C438">
+        <v>0.1313517976431735</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C439">
+        <v>0.126234681749252</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C440">
+        <v>0.1238459806349921</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C441">
+        <v>0.1170527353376047</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C442">
+        <v>0.1139390958645846</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C443">
+        <v>0.1135190918472652</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C444">
+        <v>0.1132225588298296</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C445">
+        <v>0.112750467109078</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C446">
+        <v>0.1078554736652885</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C447">
+        <v>0.1044607566346697</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C448">
+        <v>0.1040423513571407</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C449">
+        <v>0.1035960943081686</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C450">
+        <v>0.09830611010284332</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C451">
+        <v>0.09599096555618294</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C452">
+        <v>0.09189487226612755</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C453">
+        <v>0.08930697785186949</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C454">
+        <v>0.08752117447769622</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C455">
+        <v>0.08216241962371994</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C456">
+        <v>0.08188331627430911</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C457">
+        <v>0.08008871365204534</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C458">
+        <v>0.07351589781290203</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C459">
+        <v>0.06937035096119408</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C460">
+        <v>0.06426145230882217</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C461">
+        <v>0.06426145230882217</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C462">
+        <v>0.05984619527813519</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C463">
+        <v>0.0508217549899586</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C464">
+        <v>0.04128199354499737</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C465">
+        <v>0.03675794890645102</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C466">
+        <v>0.03595182455509617</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C467">
+        <v>0.03543586109142452</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C468">
+        <v>0.03366076073319257</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C469">
+        <v>0.02899297725662006</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C470">
+        <v>0.02756846167983826</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C471">
+        <v>0.0262305832206238</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C472">
+        <v>0.02450583050259573</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C473">
+        <v>0.02094825780322603</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C474">
+        <v>0.02047082906857728</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C475">
+        <v>0.01898253606681853</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C476">
+        <v>0.01898253606681853</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Paihuano</t>
+        </is>
+      </c>
+      <c r="C477">
+        <v>0.01797591227754809</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C478">
+        <v>0.01721382023853437</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C479">
+        <v>0.01583453663244647</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C480">
+        <v>0.01309835675160753</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C481">
+        <v>0.00897692929172028</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C482">
+        <v>0.007562008469449486</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C483">
+        <v>0.006982752601075344</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C484">
+        <v>0.006982752601075344</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C485">
+        <v>0.006160670280926565</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C486">
+        <v>0.006160670280926565</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C487">
+        <v>0.00598461952781352</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C488">
+        <v>0.00598461952781352</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C489">
+        <v>0.005953798523457966</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C490">
+        <v>0.0008197057256444936</v>
       </c>
     </row>
   </sheetData>
